--- a/stories/arbres/ATOM-SOC.TRA.002-05.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rosalie et papa montent dans le train. Papa montre la place. Rosalie pose ses fesses sur le siège. Elle est assise. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte. Papa dit : on reste assis, avec l'adulte. Le train roule. Rosalie tient son doudou. Elle reste assise, avec papa. Le train s'arrête. Rosalie reste assise. Papa dit : maintenant on se lève. Ils descendent ensemble.</t>
+          <t>Rosalie et papa montent dans le train. Papa montre la place. Rosalie pose ses fesses sur le siège. Elle est assise. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte. On reste assis, avec l'adulte. Le train roule. Rosalie tient son doudou. Elle reste assise, avec papa. Le train s'arrête. Rosalie reste assise. Maintenant on se lève. Ils descendent ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Rosalie et papa montent dans le train. Papa montre la place. Rosalie pose ses fesses sur le siège. Elle est assise. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte.
+papa|On reste assis, avec l'adulte.
+narrateur|Le train roule. Rosalie tient son doudou. Elle reste assise, avec papa. Le train s'arrête. Rosalie reste assise.
+papa|Maintenant on se lève. Ils descendent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Rosalie est dans le train. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Rosalie est restée assise. Papa, l'adulte, était à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1841,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ils marchent sur le quai. Rosalie tient la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2008,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2048,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.002-05.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 papa|Maintenant on se lève. Ils descendent ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Rosalie est dans le train. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Rosalie est restée assise. Papa, l'adulte, était à côté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1846,6 +1854,7 @@
           <t>narrateur|Ils marchent sur le quai. Rosalie tient la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2013,6 +2022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2055,6 +2065,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2256,6 +2280,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.TRA.002-05.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rosalie reste assise dans le train</t>
+          <t>Le train d'Amir et la rivière</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut voir la rivière depuis le train. Un sac glisse. Il reste assis. Les champs passent, puis l'eau. Ils descendent ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rosalie et papa montent dans le train. Papa montre la place. Rosalie pose ses fesses sur le siège. Elle est assise. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte. On reste assis, avec l'adulte. Le train roule. Rosalie tient son doudou. Elle reste assise, avec papa. Le train s'arrête. Rosalie reste assise. Maintenant on se lève. Ils descendent ensemble.</t>
+          <t>La gare sent le pain chaud du kiosque. Un pigeon picore une mie près du banc. Le quai tremble un peu, déjà. Le train jaune attend, portes ouvertes. Ça sent le fer chaud et le pain. Tu as vu le kiosque, Amir ? Il sent le pain. Oui. On en prendra un, à l'arrivée. Amir tient un petit sac en papier. Dedans, une pomme et un gâteau. Je veux voir la rivière. Elle arrive après les champs. On la verra par la fenêtre. En ce moment, Amir monte dans le wagon. Le plancher vibre sous ses chaussures. Voici ta place, près de la vitre. Amir pose ses fesses sur le siège. Son dos trouve le dossier tiède. Ses pieds touchent le plancher qui vibre. On reste assis, avec l'adulte. Tu restes assis, d'accord ? D'accord. Papa s'assoit tout contre lui. La porte se referme, sèche. Le wagon part sans un cri. Dehors, les toits du village reculent. Ça va vite. Oui. Tes fesses restent sur le siège. Les champs arrivent, tout jaunes. Les épis tapent le vent, dehors. Une vache lève la tête, lente. Une vache ! Tu la vois, assis. Amir colle le nez à la vitre froide. Il reste assis. Le sac glisse sous le siège d'à côté. Mon sac ! Je le prends. Papa ramène le sac sans se lever fort. Il le pose sur les genoux d'Amir. Merci. Tu es resté assis. Merci, Amir. Les champs s'en vont, tout doux. Une bande d'eau brille entre les saules. La rivière ! La voilà. Tu la regardes depuis ta place ? Oui. L'eau court, plate et claire. Un héron reste au bord, gris. Le soleil tape la vitre, puis glisse. Amir tient la pomme sans la croquer. Il reste assis, le sac sur les genoux. Un pont de fer passe au dessus de l'eau. Le wagon fait un bruit creux. On est dessus. Oui. Toi, tu restes assis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rosalie et papa montent dans le train. Papa montre la place. Rosalie pose ses fesses sur le siège. Elle est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte. Papa dit : on reste assis, avec l'adulte. Le train roule. Rosalie tient son doudou. Elle reste assise, avec papa. Le train s'arrête. Rosalie reste assise. Papa dit : maintenant on se lève. Ils descendent ensemble.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La gare sent le pain chaud du kiosque. Un pigeon picore une mie près du banc. Le quai tremble un peu, déjà. Le train jaune attend, portes ouvertes. Ça sent le fer chaud et le pain. Tu as vu le kiosque, Amir ? Il sent le pain. Oui. On en prendra un, à l'arrivée. Amir tient un petit sac en papier. Dedans, une pomme et un gâteau. Je veux voir la rivière. Elle arrive après les champs. On la verra par la fenêtre. En ce moment, Amir monte dans le wagon. Le plancher vibre sous ses chaussures. Voici ta place, près de la vitre. Amir pose ses fesses sur le siège. Son dos trouve le dossier tiède. Ses pieds touchent le plancher qui vibre. On reste assis, avec l'adulte. Tu restes assis, d'accord ? D'accord. Papa s'assoit tout contre lui. La porte se referme, sèche. Le wagon part sans un cri. Dehors, les toits du village reculent. Ça va vite. Oui. Tes fesses restent sur le siège. Les champs arrivent, tout jaunes. Les épis tapent le vent, dehors. Une vache lève la tête, lente. Une vache ! Tu la vois, assis. Amir colle le nez à la vitre froide. Il reste assis. Le sac glisse sous le siège d'à côté. Mon sac ! Je le prends. Papa ramène le sac sans se lever fort. Il le pose sur les genoux d'Amir. Merci. Tu es resté assis. Merci, Amir. Les champs s'en vont, tout doux. Une bande d'eau brille entre les saules. La rivière ! La voilà. Tu la regardes depuis ta place ? Oui. L'eau court, plate et claire. Un héron reste au bord, gris. Le soleil tape la vitre, puis glisse. Amir tient la pomme sans la croquer. Il reste assis, le sac sur les genoux. Un pont de fer passe au dessus de l'eau. Le wagon fait un bruit creux. On est dessus. Oui. Toi, tu restes assis.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Rosalie et papa montent dans le train. Papa montre la place. Rosalie pose ses fesses sur le siège. Elle est assise. Son dos est contre le dossier. Ses pieds sont sur le plancher. Papa s'assoit à côté. Papa, c'est l'adulte.
+          <t>narrateur|La gare sent le pain chaud du kiosque.
+narrateur|Un pigeon picore une mie près du banc.
+narrateur|Le quai tremble un peu, déjà.
+narrateur|Le train jaune attend, portes ouvertes.
+narrateur|Ça sent le fer chaud et le pain.
+papa|Tu as vu le kiosque, Amir ?
+enfant-m|Il sent le pain.
+papa|Oui.
+papa|On en prendra un, à l'arrivée.
+narrateur|Amir tient un petit sac en papier.
+narrateur|Dedans, une pomme et un gâteau.
+enfant-m|Je veux voir la rivière.
+papa|Elle arrive après les champs.
+papa|On la verra par la fenêtre.
+narrateur|En ce moment, Amir monte dans le wagon.
+narrateur|Le plancher vibre sous ses chaussures.
+papa|Voici ta place, près de la vitre.
+narrateur|Amir pose ses fesses sur le siège.
+narrateur|Son dos trouve le dossier tiède.
+narrateur|Ses pieds touchent le plancher qui vibre.
 papa|On reste assis, avec l'adulte.
-narrateur|Le train roule. Rosalie tient son doudou. Elle reste assise, avec papa. Le train s'arrête. Rosalie reste assise.
-papa|Maintenant on se lève. Ils descendent ensemble.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Tu restes assis, d'accord ?
+enfant-m|D'accord.
+narrateur|Papa s'assoit tout contre lui.
+narrateur|La porte se referme, sèche.
+narrateur|Le wagon part sans un cri.
+narrateur|Dehors, les toits du village reculent.
+enfant-m|Ça va vite.
+papa|Oui.
+papa|Tes fesses restent sur le siège.
+narrateur|Les champs arrivent, tout jaunes.
+narrateur|Les épis tapent le vent, dehors.
+narrateur|Une vache lève la tête, lente.
+enfant-m|Une vache !
+papa|Tu la vois, assis.
+narrateur|Amir colle le nez à la vitre froide.
+narrateur|Il reste assis.
+narrateur|Le sac glisse sous le siège d'à côté.
+enfant-m|Mon sac !
+papa|Je le prends.
+narrateur|Papa ramène le sac sans se lever fort.
+narrateur|Il le pose sur les genoux d'Amir.
+enfant-m|Merci.
+papa|Tu es resté assis.
+papa|Merci, Amir.
+narrateur|Les champs s'en vont, tout doux.
+narrateur|Une bande d'eau brille entre les saules.
+enfant-m|La rivière !
+papa|La voilà.
+papa|Tu la regardes depuis ta place ?
+enfant-m|Oui.
+narrateur|L'eau court, plate et claire.
+narrateur|Un héron reste au bord, gris.
+narrateur|Le soleil tape la vitre, puis glisse.
+narrateur|Amir tient la pomme sans la croquer.
+narrateur|Il reste assis, le sac sur les genoux.
+narrateur|Un pont de fer passe au dessus de l'eau.
+narrateur|Le wagon fait un bruit creux.
+enfant-m|On est dessus.
+papa|Oui.
+papa|Toi, tu restes assis.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>train,quai</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1416,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Rosalie est dans le train. Que fait-elle ?</t>
+          <t>Amir est dans le train. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Rosalie est dans le train. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir est dans le train. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,7 +1436,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>assis | rester assis | avec papa | avec l'adulte</t>
+          <t>assis | rester assis | il reste assis | avec papa | avec l'adulte</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1378,7 +1451,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ses fesses sont sur le siège. Avec qui ?</t>
+          <t>Ses fesses sont sur le siège. Que fait Amir ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1500,7 @@
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1503,10 +1576,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Rosalie est dans le train. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir est dans le train.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1531,12 +1604,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Rosalie est restée assise. Papa, l'adulte, était à côté.</t>
+          <t>Amir est resté assis près de la vitre. Papa, l'adulte, était juste à côté. Tes fesses étaient sur le siège. Bravo. J'ai vu la rivière. Oui, depuis ta place. Le wagon ralentit près d'un second pont. L'eau clignote encore sous le fer. On s'arrête ? Bientôt. On se lève quand je le dis. Amir serre le sac. Ses pieds restent sur le plancher. La pomme roule un peu, puis s'arrête. Tu la tiens ? Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Rosalie est restée &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e. Papa, l'adulte, était à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir est resté assis près de la vitre. Papa, l'adulte, était juste à côté. Tes fesses étaient sur le siège. Bravo. J'ai vu la rivière. Oui, depuis ta place. Le wagon ralentit près d'un second pont. L'eau clignote encore sous le fer. On s'arrête ? Bientôt. On se lève quand je le dis. Amir serre le sac. Ses pieds restent sur le plancher. La pomme roule un peu, puis s'arrête. Tu la tiens ? Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1592,7 +1665,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
@@ -1679,10 +1752,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Rosalie est restée assise. Papa, l'adulte, était à côté.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir est resté assis près de la vitre.
+narrateur|Papa, l'adulte, était juste à côté.
+papa|Tes fesses étaient sur le siège.
+papa|Bravo.
+enfant-m|J'ai vu la rivière.
+papa|Oui, depuis ta place.
+narrateur|Le wagon ralentit près d'un second pont.
+narrateur|L'eau clignote encore sous le fer.
+enfant-m|On s'arrête ?
+papa|Bientôt.
+papa|On se lève quand je le dis.
+narrateur|Amir serre le sac.
+narrateur|Ses pieds restent sur le plancher.
+narrateur|La pomme roule un peu, puis s'arrête.
+papa|Tu la tiens ?
+enfant-m|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,12 +1794,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ils marchent sur le quai. Rosalie tient la main.</t>
+          <t>Le wagon s'arrête. Le quai sent la poussière chaude. Maintenant on se lève. Tu me donnes la main ? Oui, papa. Ils descendent ensemble, pas à pas. Le kiosque de cette gare sent encore le pain. Le pain promis. Amir prend un petit pain chaud. La mie colle un peu aux doigts. Il est chaud. Comme le quai. Derrière les rails, l'eau brille encore. La rivière est encore là. Oui. Tu l'as vue, assis. Un pigeon picore une mie, déjà.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Ils marchent sur le quai. Rosalie tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le wagon s'arrête. Le quai sent la poussière chaude. Maintenant on se lève. Tu me donnes la main ? Oui, papa. Ils descendent ensemble, pas à pas. Le kiosque de cette gare sent encore le pain. Le pain promis. Amir prend un petit pain chaud. La mie colle un peu aux doigts. Il est chaud. Comme le quai. Derrière les rails, l'eau brille encore. La rivière est encore là. Oui. Tu l'as vue, assis. Un pigeon picore une mie, déjà.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1768,7 +1855,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
@@ -1851,10 +1938,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ils marchent sur le quai. Rosalie tient la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le wagon s'arrête.
+narrateur|Le quai sent la poussière chaude.
+papa|Maintenant on se lève.
+papa|Tu me donnes la main ?
+enfant-m|Oui, papa.
+narrateur|Ils descendent ensemble, pas à pas.
+narrateur|Le kiosque de cette gare sent encore le pain.
+papa|Le pain promis.
+narrateur|Amir prend un petit pain chaud.
+narrateur|La mie colle un peu aux doigts.
+enfant-m|Il est chaud.
+papa|Comme le quai.
+narrateur|Derrière les rails, l'eau brille encore.
+enfant-m|La rivière est encore là.
+papa|Oui.
+papa|Tu l'as vue, assis.
+narrateur|Un pigeon picore une mie, déjà.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1879,12 +1981,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Ils marchent sur le quai, main dans la main. Le petit pain sent le beurre. On l'a vue. Oui. Depuis ta place. Le train jaune repart, tout doux. L'eau reste entre les saules.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils marchent sur le quai, main dans la main. Le petit pain sent le beurre. On l'a vue. Oui. Depuis ta place. Le train jaune repart, tout doux. L'eau reste entre les saules.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1940,7 +2042,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
@@ -2019,10 +2121,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Ils marchent sur le quai, main dans la main.
+narrateur|Le petit pain sent le beurre.
+enfant-m|On l'a vue.
+papa|Oui.
+papa|Depuis ta place.
+narrateur|Le train jaune repart, tout doux.
+narrateur|L'eau reste entre les saules.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2041,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2079,6 +2186,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.002-05.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>train</t>
+          <t>train, champs puis rivière</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rosalie, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
